--- a/datos_nino_mensual_LE.xlsx
+++ b/datos_nino_mensual_LE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://intaarg-my.sharepoint.com/personal/lewczuk_nuria_inta_gob_ar/Documents/shiny_app/app_EMCBalcarce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="301" documentId="8_{D6F50C59-027A-4885-8A20-DA8410D8D698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A247E0F-E69A-4E71-BE29-884AFD035707}"/>
+  <xr:revisionPtr revIDLastSave="302" documentId="8_{D6F50C59-027A-4885-8A20-DA8410D8D698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A58DE16-1D42-4F77-8D26-3F98E175B8F3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8120B771-92F1-4794-9EFD-C5F0B4C6029F}"/>
   </bookViews>
@@ -404,7 +404,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2915E338-8BAB-410F-8D2B-2FCCE170B7B1}" name="Tabla1" displayName="Tabla1" ref="A1:O445" totalsRowShown="0" headerRowDxfId="8">
-  <autoFilter ref="A1:O445" xr:uid="{2915E338-8BAB-410F-8D2B-2FCCE170B7B1}"/>
+  <autoFilter ref="A1:O445" xr:uid="{2915E338-8BAB-410F-8D2B-2FCCE170B7B1}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Balcarce"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{8D58C604-7B9B-4E56-AE4E-E53465BD2FCA}" name="Año"/>
     <tableColumn id="2" xr3:uid="{8ED663FD-F228-4716-B726-5F338E03DD57}" name="Localidad"/>
@@ -4615,7 +4621,7 @@
         <v>66.279069767441854</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>1982</v>
       </c>
@@ -4662,7 +4668,7 @@
         <v>148.83720930232559</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>1987</v>
       </c>
@@ -4709,7 +4715,7 @@
         <v>-46.511627906976742</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>1991</v>
       </c>
@@ -4756,7 +4762,7 @@
         <v>139.65517241379311</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>1994</v>
       </c>
@@ -4803,7 +4809,7 @@
         <v>43.103448275862064</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>1997</v>
       </c>
@@ -4850,7 +4856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>2002</v>
       </c>
@@ -4897,7 +4903,7 @@
         <v>-68.965517241379317</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>2004</v>
       </c>
@@ -4944,7 +4950,7 @@
         <v>-48.275862068965516</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>2015</v>
       </c>
@@ -4991,7 +4997,7 @@
         <v>-36.206896551724135</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>2023</v>
       </c>
@@ -5038,7 +5044,7 @@
         <v>-37.931034482758619</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>1982</v>
       </c>
@@ -5085,7 +5091,7 @@
         <v>148.88888888888889</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>1987</v>
       </c>
@@ -5132,7 +5138,7 @@
         <v>171.11111111111111</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>1991</v>
       </c>
@@ -5179,7 +5185,7 @@
         <v>-16.666666666666664</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>1994</v>
       </c>
@@ -5226,7 +5232,7 @@
         <v>1.6666666666666667</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>1997</v>
       </c>
@@ -5273,7 +5279,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>2002</v>
       </c>
@@ -5320,7 +5326,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>2004</v>
       </c>
@@ -5367,7 +5373,7 @@
         <v>33.333333333333329</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>2015</v>
       </c>
@@ -5414,7 +5420,7 @@
         <v>36.666666666666664</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>2023</v>
       </c>
@@ -5461,7 +5467,7 @@
         <v>171.66666666666666</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>1982</v>
       </c>
@@ -5508,7 +5514,7 @@
         <v>-30.952380952380953</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>1987</v>
       </c>
@@ -5555,7 +5561,7 @@
         <v>40.476190476190474</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>1991</v>
       </c>
@@ -5602,7 +5608,7 @@
         <v>-67.346938775510196</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>1994</v>
       </c>
@@ -5649,7 +5655,7 @@
         <v>-77.551020408163268</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>1997</v>
       </c>
@@ -5696,7 +5702,7 @@
         <v>69.387755102040813</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>2002</v>
       </c>
@@ -5743,7 +5749,7 @@
         <v>79.591836734693871</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>2004</v>
       </c>
@@ -5790,7 +5796,7 @@
         <v>112.24489795918366</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>2015</v>
       </c>
@@ -5837,7 +5843,7 @@
         <v>202.0408163265306</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>2023</v>
       </c>
@@ -5884,7 +5890,7 @@
         <v>-24.489795918367346</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>1982</v>
       </c>
@@ -5931,7 +5937,7 @@
         <v>163.15789473684211</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>1987</v>
       </c>
@@ -5978,7 +5984,7 @@
         <v>-26.315789473684209</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>1991</v>
       </c>
@@ -6025,7 +6031,7 @@
         <v>28.571428571428569</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>1994</v>
       </c>
@@ -6072,7 +6078,7 @@
         <v>33.928571428571431</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>1997</v>
       </c>
@@ -6119,7 +6125,7 @@
         <v>-32.142857142857146</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>2002</v>
       </c>
@@ -6166,7 +6172,7 @@
         <v>116.07142857142858</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>2004</v>
       </c>
@@ -6213,7 +6219,7 @@
         <v>-39.285714285714285</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>2015</v>
       </c>
@@ -6260,7 +6266,7 @@
         <v>-78.571428571428569</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>2023</v>
       </c>
@@ -6307,7 +6313,7 @@
         <v>-37.5</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>1982</v>
       </c>
@@ -6354,7 +6360,7 @@
         <v>55.000000000000007</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>1987</v>
       </c>
@@ -6401,7 +6407,7 @@
         <v>57.499999999999993</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>1991</v>
       </c>
@@ -6448,7 +6454,7 @@
         <v>161.11111111111111</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>1994</v>
       </c>
@@ -6495,7 +6501,7 @@
         <v>120.83333333333333</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>1997</v>
       </c>
@@ -6542,7 +6548,7 @@
         <v>8.3333333333333321</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>2002</v>
       </c>
@@ -6589,7 +6595,7 @@
         <v>281.94444444444446</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>2004</v>
       </c>
@@ -6636,7 +6642,7 @@
         <v>-30.555555555555557</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>2015</v>
       </c>
@@ -6683,7 +6689,7 @@
         <v>31.944444444444443</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>2023</v>
       </c>
@@ -6730,7 +6736,7 @@
         <v>-72.222222222222214</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>1982</v>
       </c>
@@ -6777,7 +6783,7 @@
         <v>-11.267605633802818</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>1987</v>
       </c>
@@ -6824,7 +6830,7 @@
         <v>-56.338028169014088</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>1991</v>
       </c>
@@ -6871,7 +6877,7 @@
         <v>-37.5</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>1994</v>
       </c>
@@ -6918,7 +6924,7 @@
         <v>-73.611111111111114</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>1997</v>
       </c>
@@ -6965,7 +6971,7 @@
         <v>101.38888888888889</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>2002</v>
       </c>
@@ -7012,7 +7018,7 @@
         <v>2.7777777777777777</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>2004</v>
       </c>
@@ -7059,7 +7065,7 @@
         <v>4.1666666666666661</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2015</v>
       </c>
@@ -7106,7 +7112,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>2023</v>
       </c>
@@ -7153,7 +7159,7 @@
         <v>-8.3333333333333321</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>1982</v>
       </c>
@@ -7200,7 +7206,7 @@
         <v>23.711340206185564</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>1987</v>
       </c>
@@ -7247,7 +7253,7 @@
         <v>35.051546391752574</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>1991</v>
       </c>
@@ -7294,7 +7300,7 @@
         <v>-4.4444444444444446</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>1994</v>
       </c>
@@ -7341,7 +7347,7 @@
         <v>1.1111111111111112</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>1997</v>
       </c>
@@ -7388,7 +7394,7 @@
         <v>43.333333333333336</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>2002</v>
       </c>
@@ -7435,7 +7441,7 @@
         <v>-37.777777777777779</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>2004</v>
       </c>
@@ -7482,7 +7488,7 @@
         <v>-36.666666666666664</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2015</v>
       </c>
@@ -7529,7 +7535,7 @@
         <v>-85.555555555555557</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2023</v>
       </c>
@@ -7576,7 +7582,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>1982</v>
       </c>
@@ -7623,7 +7629,7 @@
         <v>56.730769230769226</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>1987</v>
       </c>
@@ -7670,7 +7676,7 @@
         <v>-19.230769230769234</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>1991</v>
       </c>
@@ -7717,7 +7723,7 @@
         <v>16.483516483516482</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>1994</v>
       </c>
@@ -7764,7 +7770,7 @@
         <v>39.560439560439562</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>1997</v>
       </c>
@@ -7811,7 +7817,7 @@
         <v>9.8901098901098905</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2002</v>
       </c>
@@ -7858,7 +7864,7 @@
         <v>9.8901098901098905</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2004</v>
       </c>
@@ -7905,7 +7911,7 @@
         <v>-16.483516483516482</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2015</v>
       </c>
@@ -7952,7 +7958,7 @@
         <v>131.86813186813185</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2023</v>
       </c>
@@ -7999,7 +8005,7 @@
         <v>-57.142857142857139</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>1982</v>
       </c>
@@ -8046,7 +8052,7 @@
         <v>-68.571428571428569</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>1987</v>
       </c>
@@ -8093,7 +8099,7 @@
         <v>-54.285714285714285</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>1991</v>
       </c>
@@ -8140,7 +8146,7 @@
         <v>215.11627906976742</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>1994</v>
       </c>
@@ -8187,7 +8193,7 @@
         <v>-18.604651162790699</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>1997</v>
       </c>
@@ -8234,7 +8240,7 @@
         <v>-45.348837209302324</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>2002</v>
       </c>
@@ -8281,7 +8287,7 @@
         <v>-11.627906976744185</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2004</v>
       </c>
@@ -8328,7 +8334,7 @@
         <v>43.02325581395349</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>2015</v>
       </c>
@@ -8375,7 +8381,7 @@
         <v>96.511627906976756</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2023</v>
       </c>
@@ -8422,7 +8428,7 @@
         <v>32.558139534883722</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>1982</v>
       </c>
@@ -8469,7 +8475,7 @@
         <v>53.125</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>1987</v>
       </c>
@@ -8516,7 +8522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>1991</v>
       </c>
@@ -8563,7 +8569,7 @@
         <v>275.67567567567568</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>1994</v>
       </c>
@@ -8610,7 +8616,7 @@
         <v>-2.7027027027027026</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>1997</v>
       </c>
@@ -8657,7 +8663,7 @@
         <v>135.13513513513513</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2002</v>
       </c>
@@ -8704,7 +8710,7 @@
         <v>-83.78378378378379</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>2004</v>
       </c>
@@ -8751,7 +8757,7 @@
         <v>-18.918918918918919</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2015</v>
       </c>
@@ -8798,7 +8804,7 @@
         <v>5.4054054054054053</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>2023</v>
       </c>
@@ -8845,7 +8851,7 @@
         <v>-2.7027027027027026</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>1982</v>
       </c>
@@ -8892,7 +8898,7 @@
         <v>37.931034482758619</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>1987</v>
       </c>
@@ -8939,7 +8945,7 @@
         <v>272.41379310344826</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>1991</v>
       </c>
@@ -8986,7 +8992,7 @@
         <v>-63.888888888888886</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>1994</v>
       </c>
@@ -9033,7 +9039,7 @@
         <v>69.444444444444443</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>1997</v>
       </c>
@@ -9080,7 +9086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>2002</v>
       </c>
@@ -9127,7 +9133,7 @@
         <v>33.333333333333329</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>2004</v>
       </c>
@@ -9174,7 +9180,7 @@
         <v>172.22222222222223</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>2015</v>
       </c>
@@ -9221,7 +9227,7 @@
         <v>69.444444444444443</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>2023</v>
       </c>
@@ -9268,7 +9274,7 @@
         <v>47.222222222222221</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>1982</v>
       </c>
@@ -9315,7 +9321,7 @@
         <v>-64.705882352941174</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>1987</v>
       </c>
@@ -9362,7 +9368,7 @@
         <v>2.9411764705882351</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>1991</v>
       </c>
@@ -9409,7 +9415,7 @@
         <v>-64.705882352941174</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>1994</v>
       </c>
@@ -9456,7 +9462,7 @@
         <v>-41.17647058823529</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>1997</v>
       </c>
@@ -9503,7 +9509,7 @@
         <v>158.8235294117647</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>2002</v>
       </c>
@@ -9550,7 +9556,7 @@
         <v>185.29411764705884</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>2004</v>
       </c>
@@ -9597,7 +9603,7 @@
         <v>147.05882352941177</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>2015</v>
       </c>
@@ -9644,7 +9650,7 @@
         <v>352.94117647058823</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>2023</v>
       </c>
@@ -9691,7 +9697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>1982</v>
       </c>
@@ -9738,7 +9744,7 @@
         <v>152.38095238095238</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>1987</v>
       </c>
@@ -9785,7 +9791,7 @@
         <v>-57.142857142857139</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>1991</v>
       </c>
@@ -9832,7 +9838,7 @@
         <v>46.938775510204081</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>1994</v>
       </c>
@@ -9879,7 +9885,7 @@
         <v>-18.367346938775512</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>1997</v>
       </c>
@@ -9926,7 +9932,7 @@
         <v>-36.734693877551024</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>2002</v>
       </c>
@@ -9973,7 +9979,7 @@
         <v>77.551020408163268</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>2004</v>
       </c>
@@ -10020,7 +10026,7 @@
         <v>-42.857142857142854</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>2015</v>
       </c>
@@ -10067,7 +10073,7 @@
         <v>-79.591836734693871</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>2023</v>
       </c>
@@ -10114,7 +10120,7 @@
         <v>30.612244897959183</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>1982</v>
       </c>
@@ -10161,7 +10167,7 @@
         <v>52.12765957446809</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>1987</v>
       </c>
@@ -10208,7 +10214,7 @@
         <v>4.2553191489361701</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>1991</v>
       </c>
@@ -10255,7 +10261,7 @@
         <v>39.189189189189186</v>
       </c>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>1994</v>
       </c>
@@ -10302,7 +10308,7 @@
         <v>25.675675675675674</v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>1997</v>
       </c>
@@ -10349,7 +10355,7 @@
         <v>248.64864864864865</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>2002</v>
       </c>
@@ -10396,7 +10402,7 @@
         <v>163.51351351351352</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>2004</v>
       </c>
@@ -10443,7 +10449,7 @@
         <v>-24.324324324324326</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>2015</v>
       </c>
@@ -10490,7 +10496,7 @@
         <v>9.4594594594594597</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>2023</v>
       </c>
@@ -10537,7 +10543,7 @@
         <v>13.513513513513514</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>1982</v>
       </c>
@@ -10584,7 +10590,7 @@
         <v>-17.567567567567568</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>1987</v>
       </c>
@@ -10631,7 +10637,7 @@
         <v>58.108108108108105</v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>1991</v>
       </c>
@@ -10678,7 +10684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>1994</v>
       </c>
@@ -10725,7 +10731,7 @@
         <v>-71.910112359550567</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>1997</v>
       </c>
@@ -10772,7 +10778,7 @@
         <v>-26.966292134831459</v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>2002</v>
       </c>
@@ -10819,7 +10825,7 @@
         <v>79.775280898876403</v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>2004</v>
       </c>
@@ -10866,7 +10872,7 @@
         <v>-40.449438202247187</v>
       </c>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>2015</v>
       </c>
@@ -10913,7 +10919,7 @@
         <v>64.044943820224717</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>2023</v>
       </c>
@@ -10960,7 +10966,7 @@
         <v>65.168539325842701</v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>1982</v>
       </c>
@@ -11007,7 +11013,7 @@
         <v>83.82352941176471</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>1987</v>
       </c>
@@ -11054,7 +11060,7 @@
         <v>36.764705882352942</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>1991</v>
       </c>
@@ -11101,7 +11107,7 @@
         <v>93.333333333333329</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>1994</v>
       </c>
@@ -11148,7 +11154,7 @@
         <v>133.33333333333331</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>1997</v>
       </c>
@@ -11195,7 +11201,7 @@
         <v>55.000000000000007</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>2002</v>
       </c>
@@ -11242,7 +11248,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>2004</v>
       </c>
@@ -11289,7 +11295,7 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>2015</v>
       </c>
@@ -11336,7 +11342,7 @@
         <v>-55.000000000000007</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>2023</v>
       </c>
@@ -11383,7 +11389,7 @@
         <v>301.66666666666669</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>1982</v>
       </c>
@@ -11430,7 +11436,7 @@
         <v>59.595959595959592</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>1987</v>
       </c>
@@ -11477,7 +11483,7 @@
         <v>16.161616161616163</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>1991</v>
       </c>
@@ -11524,7 +11530,7 @@
         <v>46.875</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>1994</v>
       </c>
@@ -11571,7 +11577,7 @@
         <v>-40.625</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>1997</v>
       </c>
@@ -11618,7 +11624,7 @@
         <v>68.75</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>2002</v>
       </c>
@@ -11665,7 +11671,7 @@
         <v>-15.625</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>2004</v>
       </c>
@@ -11712,7 +11718,7 @@
         <v>-62.5</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>2015</v>
       </c>
@@ -11759,7 +11765,7 @@
         <v>77.083333333333343</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>2023</v>
       </c>
@@ -11806,7 +11812,7 @@
         <v>-48.958333333333329</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>1982</v>
       </c>
@@ -11853,7 +11859,7 @@
         <v>59.210526315789465</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>1987</v>
       </c>
@@ -11900,7 +11906,7 @@
         <v>-9.2105263157894726</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>1991</v>
       </c>
@@ -11947,7 +11953,7 @@
         <v>55.102040816326522</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>1994</v>
       </c>
@@ -11994,7 +12000,7 @@
         <v>-22.448979591836736</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>1997</v>
       </c>
@@ -12041,7 +12047,7 @@
         <v>-55.102040816326522</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>2002</v>
       </c>
@@ -12088,7 +12094,7 @@
         <v>17.346938775510203</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>2004</v>
       </c>
@@ -12135,7 +12141,7 @@
         <v>51.020408163265309</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>2015</v>
       </c>
@@ -12182,7 +12188,7 @@
         <v>124.48979591836735</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>2023</v>
       </c>
@@ -12229,7 +12235,7 @@
         <v>40.816326530612244</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>1987</v>
       </c>
@@ -12268,7 +12274,7 @@
       <c r="N245" s="3"/>
       <c r="O245" s="3"/>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>1991</v>
       </c>
@@ -12315,7 +12321,7 @@
         <v>448.27586206896547</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>1994</v>
       </c>
@@ -12362,7 +12368,7 @@
         <v>-37.931034482758619</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>1997</v>
       </c>
@@ -12409,7 +12415,7 @@
         <v>189.65517241379311</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>2002</v>
       </c>
@@ -12456,7 +12462,7 @@
         <v>-86.206896551724128</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>2004</v>
       </c>
@@ -12503,7 +12509,7 @@
         <v>-3.4482758620689653</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>2015</v>
       </c>
@@ -12550,7 +12556,7 @@
         <v>20.689655172413794</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>2023</v>
       </c>
@@ -12597,7 +12603,7 @@
         <v>10.344827586206897</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>1987</v>
       </c>
@@ -12636,7 +12642,7 @@
       <c r="N253" s="3"/>
       <c r="O253" s="3"/>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>1991</v>
       </c>
@@ -12683,7 +12689,7 @@
         <v>-65.625</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>1994</v>
       </c>
@@ -12730,7 +12736,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>1997</v>
       </c>
@@ -12777,7 +12783,7 @@
         <v>-18.75</v>
       </c>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>2002</v>
       </c>
@@ -12824,7 +12830,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>2004</v>
       </c>
@@ -12871,7 +12877,7 @@
         <v>131.25</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>2015</v>
       </c>
@@ -12918,7 +12924,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>2023</v>
       </c>
@@ -12965,7 +12971,7 @@
         <v>203.125</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>1987</v>
       </c>
@@ -13004,7 +13010,7 @@
       <c r="N261" s="3"/>
       <c r="O261" s="3"/>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>1991</v>
       </c>
@@ -13051,7 +13057,7 @@
         <v>-53.125</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>1994</v>
       </c>
@@ -13098,7 +13104,7 @@
         <v>-37.5</v>
       </c>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>1997</v>
       </c>
@@ -13145,7 +13151,7 @@
         <v>68.75</v>
       </c>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>2002</v>
       </c>
@@ -13192,7 +13198,7 @@
         <v>271.875</v>
       </c>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>2004</v>
       </c>
@@ -13239,7 +13245,7 @@
         <v>93.75</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>2015</v>
       </c>
@@ -13286,7 +13292,7 @@
         <v>296.875</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>2023</v>
       </c>
@@ -13333,7 +13339,7 @@
         <v>-21.875</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>1987</v>
       </c>
@@ -13372,7 +13378,7 @@
       <c r="N269" s="3"/>
       <c r="O269" s="3"/>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>1991</v>
       </c>
@@ -13419,7 +13425,7 @@
         <v>45.454545454545453</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>1994</v>
       </c>
@@ -13466,7 +13472,7 @@
         <v>-67.272727272727266</v>
       </c>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>1997</v>
       </c>
@@ -13513,7 +13519,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>2002</v>
       </c>
@@ -13560,7 +13566,7 @@
         <v>25.454545454545453</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>2004</v>
       </c>
@@ -13607,7 +13613,7 @@
         <v>-63.636363636363633</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>2015</v>
       </c>
@@ -13654,7 +13660,7 @@
         <v>-85.454545454545453</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>2023</v>
       </c>
@@ -13701,7 +13707,7 @@
         <v>38.181818181818187</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>1987</v>
       </c>
@@ -13740,7 +13746,7 @@
       <c r="N277" s="3"/>
       <c r="O277" s="3"/>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>1991</v>
       </c>
@@ -13787,7 +13793,7 @@
         <v>-12.5</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>1994</v>
       </c>
@@ -13834,7 +13840,7 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>1997</v>
       </c>
@@ -13881,7 +13887,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>2002</v>
       </c>
@@ -13928,7 +13934,7 @@
         <v>86.25</v>
       </c>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>2004</v>
       </c>
@@ -13975,7 +13981,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>2015</v>
       </c>
@@ -14022,7 +14028,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>2023</v>
       </c>
@@ -14069,7 +14075,7 @@
         <v>41.25</v>
       </c>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>1987</v>
       </c>
@@ -14116,7 +14122,7 @@
         <v>27.173913043478258</v>
       </c>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>1991</v>
       </c>
@@ -14163,7 +14169,7 @@
         <v>32.53012048192771</v>
       </c>
     </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>1994</v>
       </c>
@@ -14210,7 +14216,7 @@
         <v>-50.602409638554214</v>
       </c>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>1997</v>
       </c>
@@ -14257,7 +14263,7 @@
         <v>-14.457831325301203</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>2002</v>
       </c>
@@ -14304,7 +14310,7 @@
         <v>68.674698795180717</v>
       </c>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>2004</v>
       </c>
@@ -14351,7 +14357,7 @@
         <v>-13.253012048192772</v>
       </c>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>2015</v>
       </c>
@@ -14398,7 +14404,7 @@
         <v>-57.831325301204814</v>
       </c>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>2023</v>
       </c>
@@ -14445,7 +14451,7 @@
         <v>77.108433734939766</v>
       </c>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>1987</v>
       </c>
@@ -14492,7 +14498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>1991</v>
       </c>
@@ -14539,7 +14545,7 @@
         <v>213.55932203389833</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>1994</v>
       </c>
@@ -14586,7 +14592,7 @@
         <v>154.23728813559322</v>
       </c>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>1997</v>
       </c>
@@ -14633,7 +14639,7 @@
         <v>11.864406779661017</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>2002</v>
       </c>
@@ -14680,7 +14686,7 @@
         <v>-5.0847457627118651</v>
       </c>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>2004</v>
       </c>
@@ -14727,7 +14733,7 @@
         <v>86.440677966101703</v>
       </c>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>2015</v>
       </c>
@@ -14774,7 +14780,7 @@
         <v>-11.864406779661017</v>
       </c>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>2023</v>
       </c>
@@ -14821,7 +14827,7 @@
         <v>374.57627118644064</v>
       </c>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>1987</v>
       </c>
@@ -14868,7 +14874,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>1991</v>
       </c>
@@ -14915,7 +14921,7 @@
         <v>129.34782608695653</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>1994</v>
       </c>
@@ -14962,7 +14968,7 @@
         <v>-38.04347826086957</v>
       </c>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>1997</v>
       </c>
@@ -15009,7 +15015,7 @@
         <v>164.13043478260869</v>
       </c>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>2002</v>
       </c>
@@ -15056,7 +15062,7 @@
         <v>-34.782608695652172</v>
       </c>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>2004</v>
       </c>
@@ -15103,7 +15109,7 @@
         <v>-33.695652173913047</v>
       </c>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>2015</v>
       </c>
@@ -15150,7 +15156,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>2023</v>
       </c>
@@ -15197,7 +15203,7 @@
         <v>-86.956521739130437</v>
       </c>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>1987</v>
       </c>
@@ -15244,7 +15250,7 @@
         <v>-20.689655172413794</v>
       </c>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>1991</v>
       </c>
@@ -15291,7 +15297,7 @@
         <v>196.62921348314606</v>
       </c>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>1994</v>
       </c>
@@ -15338,7 +15344,7 @@
         <v>-58.426966292134829</v>
       </c>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>1997</v>
       </c>
@@ -15385,7 +15391,7 @@
         <v>14.606741573033707</v>
       </c>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>2002</v>
       </c>
@@ -15432,7 +15438,7 @@
         <v>-6.7415730337078648</v>
       </c>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>2004</v>
       </c>
@@ -15479,7 +15485,7 @@
         <v>23.595505617977526</v>
       </c>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>2015</v>
       </c>
@@ -15526,7 +15532,7 @@
         <v>85.393258426966284</v>
       </c>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>2023</v>
       </c>
@@ -15573,7 +15579,7 @@
         <v>70.786516853932582</v>
       </c>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>1982</v>
       </c>
@@ -15620,7 +15626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>1987</v>
       </c>
@@ -15667,7 +15673,7 @@
         <v>44.444444444444443</v>
       </c>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>1991</v>
       </c>
@@ -15714,7 +15720,7 @@
         <v>261.11111111111114</v>
       </c>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>1994</v>
       </c>
@@ -15761,7 +15767,7 @@
         <v>13.888888888888889</v>
       </c>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>1997</v>
       </c>
@@ -15808,7 +15814,7 @@
         <v>186.11111111111111</v>
       </c>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>2002</v>
       </c>
@@ -15855,7 +15861,7 @@
         <v>-83.333333333333343</v>
       </c>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>2004</v>
       </c>
@@ -15902,7 +15908,7 @@
         <v>5.5555555555555554</v>
       </c>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>2015</v>
       </c>
@@ -15949,7 +15955,7 @@
         <v>-30.555555555555557</v>
       </c>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>2023</v>
       </c>
@@ -15996,7 +16002,7 @@
         <v>-36.111111111111107</v>
       </c>
     </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>1982</v>
       </c>
@@ -16043,7 +16049,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>1987</v>
       </c>
@@ -16090,7 +16096,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>1991</v>
       </c>
@@ -16137,7 +16143,7 @@
         <v>-47.058823529411761</v>
       </c>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>1994</v>
       </c>
@@ -16184,7 +16190,7 @@
         <v>-55.882352941176471</v>
       </c>
     </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>1997</v>
       </c>
@@ -16231,7 +16237,7 @@
         <v>29.411764705882355</v>
       </c>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>2002</v>
       </c>
@@ -16278,7 +16284,7 @@
         <v>82.35294117647058</v>
       </c>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>2004</v>
       </c>
@@ -16325,7 +16331,7 @@
         <v>129.41176470588235</v>
       </c>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>2015</v>
       </c>
@@ -16372,7 +16378,7 @@
         <v>52.941176470588239</v>
       </c>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>2023</v>
       </c>
@@ -16419,7 +16425,7 @@
         <v>79.411764705882348</v>
       </c>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>1982</v>
       </c>
@@ -16466,7 +16472,7 @@
         <v>-81.081081081081081</v>
       </c>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>1987</v>
       </c>
@@ -16513,7 +16519,7 @@
         <v>16.216216216216218</v>
       </c>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>1991</v>
       </c>
@@ -16560,7 +16566,7 @@
         <v>-3.3333333333333335</v>
       </c>
     </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>1994</v>
       </c>
@@ -16607,7 +16613,7 @@
         <v>-26.666666666666668</v>
       </c>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>1997</v>
       </c>
@@ -16654,7 +16660,7 @@
         <v>123.33333333333334</v>
       </c>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>2002</v>
       </c>
@@ -16701,7 +16707,7 @@
         <v>313.33333333333331</v>
       </c>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>2004</v>
       </c>
@@ -16748,7 +16754,7 @@
         <v>273.33333333333331</v>
       </c>
     </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>2015</v>
       </c>
@@ -16795,7 +16801,7 @@
         <v>296.66666666666669</v>
       </c>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>2023</v>
       </c>
@@ -16842,7 +16848,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>1982</v>
       </c>
@@ -16889,7 +16895,7 @@
         <v>127.45098039215685</v>
       </c>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>1987</v>
       </c>
@@ -16936,7 +16942,7 @@
         <v>-45.098039215686278</v>
       </c>
     </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>1991</v>
       </c>
@@ -16983,7 +16989,7 @@
         <v>15.254237288135593</v>
       </c>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>1994</v>
       </c>
@@ -17030,7 +17036,7 @@
         <v>-22.033898305084744</v>
       </c>
     </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>1997</v>
       </c>
@@ -17077,7 +17083,7 @@
         <v>-74.576271186440678</v>
       </c>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>2002</v>
       </c>
@@ -17124,7 +17130,7 @@
         <v>50.847457627118644</v>
       </c>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>2004</v>
       </c>
@@ -17171,7 +17177,7 @@
         <v>-71.186440677966104</v>
       </c>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>2015</v>
       </c>
@@ -17218,7 +17224,7 @@
         <v>-83.050847457627114</v>
       </c>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>2023</v>
       </c>
@@ -17265,7 +17271,7 @@
         <v>-33.898305084745758</v>
       </c>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>1982</v>
       </c>
@@ -17312,7 +17318,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>1987</v>
       </c>
@@ -17359,7 +17365,7 @@
         <v>-7.5</v>
       </c>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>1991</v>
       </c>
@@ -17406,7 +17412,7 @@
         <v>-30.76923076923077</v>
       </c>
     </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>1994</v>
       </c>
@@ -17453,7 +17459,7 @@
         <v>65.384615384615387</v>
       </c>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>1997</v>
       </c>
@@ -17500,7 +17506,7 @@
         <v>196.15384615384613</v>
       </c>
     </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>2002</v>
       </c>
@@ -17547,7 +17553,7 @@
         <v>110.25641025641026</v>
       </c>
     </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>2004</v>
       </c>
@@ -17594,7 +17600,7 @@
         <v>-15.384615384615385</v>
       </c>
     </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>2015</v>
       </c>
@@ -17641,7 +17647,7 @@
         <v>15.384615384615385</v>
       </c>
     </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>2023</v>
       </c>
@@ -17688,7 +17694,7 @@
         <v>7.6923076923076925</v>
       </c>
     </row>
-    <row r="362" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>1982</v>
       </c>
@@ -17735,7 +17741,7 @@
         <v>-18.75</v>
       </c>
     </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>1987</v>
       </c>
@@ -17782,7 +17788,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="364" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>1991</v>
       </c>
@@ -17829,7 +17835,7 @@
         <v>4.1666666666666661</v>
       </c>
     </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>1994</v>
       </c>
@@ -17876,7 +17882,7 @@
         <v>9.375</v>
       </c>
     </row>
-    <row r="366" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>1997</v>
       </c>
@@ -17923,7 +17929,7 @@
         <v>-16.666666666666664</v>
       </c>
     </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>2002</v>
       </c>
@@ -17970,7 +17976,7 @@
         <v>90.625</v>
       </c>
     </row>
-    <row r="368" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>2004</v>
       </c>
@@ -18017,7 +18023,7 @@
         <v>15.625</v>
       </c>
     </row>
-    <row r="369" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>2015</v>
       </c>
@@ -18064,7 +18070,7 @@
         <v>-20.833333333333336</v>
       </c>
     </row>
-    <row r="370" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>2023</v>
       </c>
@@ -18111,7 +18117,7 @@
         <v>60.416666666666664</v>
       </c>
     </row>
-    <row r="371" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>1982</v>
       </c>
@@ -18158,7 +18164,7 @@
         <v>-37.349397590361441</v>
       </c>
     </row>
-    <row r="372" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>1987</v>
       </c>
@@ -18205,7 +18211,7 @@
         <v>33.734939759036145</v>
       </c>
     </row>
-    <row r="373" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>1991</v>
       </c>
@@ -18252,7 +18258,7 @@
         <v>122.85714285714286</v>
       </c>
     </row>
-    <row r="374" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>1994</v>
       </c>
@@ -18299,7 +18305,7 @@
         <v>75.714285714285708</v>
       </c>
     </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>1997</v>
       </c>
@@ -18346,7 +18352,7 @@
         <v>44.285714285714285</v>
       </c>
     </row>
-    <row r="376" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>2002</v>
       </c>
@@ -18393,7 +18399,7 @@
         <v>12.857142857142856</v>
       </c>
     </row>
-    <row r="377" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>2004</v>
       </c>
@@ -18440,7 +18446,7 @@
         <v>54.285714285714285</v>
       </c>
     </row>
-    <row r="378" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>2015</v>
       </c>
@@ -18487,7 +18493,7 @@
         <v>-48.571428571428569</v>
       </c>
     </row>
-    <row r="379" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>2023</v>
       </c>
@@ -18534,7 +18540,7 @@
         <v>291.42857142857139</v>
       </c>
     </row>
-    <row r="380" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>1982</v>
       </c>
@@ -18581,7 +18587,7 @@
         <v>-44.444444444444443</v>
       </c>
     </row>
-    <row r="381" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>1987</v>
       </c>
@@ -18628,7 +18634,7 @@
         <v>62.698412698412696</v>
       </c>
     </row>
-    <row r="382" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>1991</v>
       </c>
@@ -18675,7 +18681,7 @@
         <v>40.196078431372548</v>
       </c>
     </row>
-    <row r="383" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>1994</v>
       </c>
@@ -18722,7 +18728,7 @@
         <v>-38.235294117647058</v>
       </c>
     </row>
-    <row r="384" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>1997</v>
       </c>
@@ -18769,7 +18775,7 @@
         <v>82.35294117647058</v>
       </c>
     </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>2002</v>
       </c>
@@ -18816,7 +18822,7 @@
         <v>-47.058823529411761</v>
       </c>
     </row>
-    <row r="386" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>2004</v>
       </c>
@@ -18863,7 +18869,7 @@
         <v>-47.058823529411761</v>
       </c>
     </row>
-    <row r="387" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>2015</v>
       </c>
@@ -18910,7 +18916,7 @@
         <v>-41.17647058823529</v>
       </c>
     </row>
-    <row r="388" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>2023</v>
       </c>
@@ -18957,7 +18963,7 @@
         <v>-61.764705882352942</v>
       </c>
     </row>
-    <row r="389" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>1982</v>
       </c>
@@ -19004,7 +19010,7 @@
         <v>-33.734939759036145</v>
       </c>
     </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>1987</v>
       </c>
@@ -19051,7 +19057,7 @@
         <v>28.915662650602407</v>
       </c>
     </row>
-    <row r="391" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>1991</v>
       </c>
@@ -19098,7 +19104,7 @@
         <v>140.69767441860466</v>
       </c>
     </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>1994</v>
       </c>
@@ -19145,7 +19151,7 @@
         <v>-10.465116279069768</v>
       </c>
     </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>1997</v>
       </c>
@@ -19192,7 +19198,7 @@
         <v>-8.1395348837209305</v>
       </c>
     </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>2002</v>
       </c>
@@ -19239,7 +19245,7 @@
         <v>27.906976744186046</v>
       </c>
     </row>
-    <row r="395" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>2004</v>
       </c>
@@ -19286,7 +19292,7 @@
         <v>30.232558139534881</v>
       </c>
     </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>2015</v>
       </c>
@@ -19333,7 +19339,7 @@
         <v>141.86046511627907</v>
       </c>
     </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>2023</v>
       </c>
@@ -19380,7 +19386,7 @@
         <v>66.279069767441854</v>
       </c>
     </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>2015</v>
       </c>
@@ -19430,7 +19436,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="399" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>2023</v>
       </c>
@@ -19480,7 +19486,7 @@
         <v>-30.1</v>
       </c>
     </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>2015</v>
       </c>
@@ -19530,7 +19536,7 @@
         <v>160.1</v>
       </c>
     </row>
-    <row r="401" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>2023</v>
       </c>
@@ -19580,7 +19586,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="402" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>2015</v>
       </c>
@@ -19630,7 +19636,7 @@
         <v>-40.5</v>
       </c>
     </row>
-    <row r="403" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>2023</v>
       </c>
@@ -19680,7 +19686,7 @@
         <v>125.7</v>
       </c>
     </row>
-    <row r="404" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>2015</v>
       </c>
@@ -19730,7 +19736,7 @@
         <v>-99</v>
       </c>
     </row>
-    <row r="405" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>2023</v>
       </c>
@@ -19780,7 +19786,7 @@
         <v>-40.200000000000003</v>
       </c>
     </row>
-    <row r="406" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>2015</v>
       </c>
@@ -19830,7 +19836,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="407" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>2023</v>
       </c>
@@ -19880,7 +19886,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="408" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>2015</v>
       </c>
@@ -19930,7 +19936,7 @@
         <v>55.7</v>
       </c>
     </row>
-    <row r="409" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>2023</v>
       </c>
@@ -19980,7 +19986,7 @@
         <v>-2.1</v>
       </c>
     </row>
-    <row r="410" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>2015</v>
       </c>
@@ -20030,7 +20036,7 @@
         <v>-21.7</v>
       </c>
     </row>
-    <row r="411" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>2023</v>
       </c>
@@ -20080,7 +20086,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="412" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>2015</v>
       </c>
@@ -20130,7 +20136,7 @@
         <v>-54.2</v>
       </c>
     </row>
-    <row r="413" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>2023</v>
       </c>
@@ -20180,7 +20186,7 @@
         <v>74.3</v>
       </c>
     </row>
-    <row r="414" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>2015</v>
       </c>
@@ -20230,7 +20236,7 @@
         <v>-80.8</v>
       </c>
     </row>
-    <row r="415" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>2023</v>
       </c>
@@ -20280,7 +20286,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="416" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>2015</v>
       </c>
@@ -20330,7 +20336,7 @@
         <v>-63.9</v>
       </c>
     </row>
-    <row r="417" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>2023</v>
       </c>
@@ -20380,7 +20386,7 @@
         <v>55.9</v>
       </c>
     </row>
-    <row r="418" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>2015</v>
       </c>
@@ -20430,7 +20436,7 @@
         <v>96.1</v>
       </c>
     </row>
-    <row r="419" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>2023</v>
       </c>
@@ -20480,7 +20486,7 @@
         <v>-75</v>
       </c>
     </row>
-    <row r="420" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>2015</v>
       </c>
@@ -20530,7 +20536,7 @@
         <v>-50.2</v>
       </c>
     </row>
-    <row r="421" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>2023</v>
       </c>
@@ -20580,7 +20586,7 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="422" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>2015</v>
       </c>
@@ -20630,7 +20636,7 @@
         <v>-91.9</v>
       </c>
     </row>
-    <row r="423" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>2023</v>
       </c>
@@ -20680,7 +20686,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="424" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>2015</v>
       </c>
@@ -20730,7 +20736,7 @@
         <v>897.2</v>
       </c>
     </row>
-    <row r="425" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>2023</v>
       </c>
@@ -20780,7 +20786,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="426" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>2015</v>
       </c>
@@ -20830,7 +20836,7 @@
         <v>-91.9</v>
       </c>
     </row>
-    <row r="427" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>2023</v>
       </c>
@@ -20880,7 +20886,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="428" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>2015</v>
       </c>
@@ -20930,7 +20936,7 @@
         <v>-14.8</v>
       </c>
     </row>
-    <row r="429" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>2023</v>
       </c>
@@ -20980,7 +20986,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="430" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>2015</v>
       </c>
@@ -21030,7 +21036,7 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="431" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>2023</v>
       </c>
@@ -21072,7 +21078,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="432" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>2015</v>
       </c>
@@ -21122,7 +21128,7 @@
         <v>37.6</v>
       </c>
     </row>
-    <row r="433" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>2023</v>
       </c>
@@ -21172,7 +21178,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="434" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>2015</v>
       </c>
@@ -21222,7 +21228,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="435" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>2023</v>
       </c>
@@ -21272,7 +21278,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="436" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>2015</v>
       </c>
@@ -21322,7 +21328,7 @@
         <v>-93.5</v>
       </c>
     </row>
-    <row r="437" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>2023</v>
       </c>
@@ -21372,7 +21378,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="438" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>2015</v>
       </c>
@@ -21422,7 +21428,7 @@
         <v>-93</v>
       </c>
     </row>
-    <row r="439" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>2023</v>
       </c>
@@ -21472,7 +21478,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="440" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>2015</v>
       </c>
@@ -21522,7 +21528,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="441" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>2023</v>
       </c>
@@ -21572,7 +21578,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="442" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>2015</v>
       </c>
@@ -21622,7 +21628,7 @@
         <v>43.6</v>
       </c>
     </row>
-    <row r="443" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>2023</v>
       </c>
@@ -21672,7 +21678,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="444" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>2015</v>
       </c>
@@ -21722,7 +21728,7 @@
         <v>-38.200000000000003</v>
       </c>
     </row>
-    <row r="445" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>2023</v>
       </c>
